--- a/project/outputs_xlsx_solution/test33.4-wide-NB-1.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NB-1.xlsx
@@ -909,9 +909,6 @@
       <c r="DI1">
         <v>110</v>
       </c>
-      <c r="DJ1">
-        <v>111</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -1253,9 +1250,6 @@
         <v>14</v>
       </c>
       <c r="W12" t="s">
-        <v>33</v>
-      </c>
-      <c r="X12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1278,11 +1272,14 @@
       <c r="K13" t="s">
         <v>34</v>
       </c>
+      <c r="W13" t="s">
+        <v>15</v>
+      </c>
       <c r="X13" t="s">
         <v>15</v>
       </c>
       <c r="Y13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="s">
         <v>14</v>
@@ -1294,9 +1291,6 @@
         <v>14</v>
       </c>
       <c r="AC13" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1349,7 +1343,7 @@
       <c r="U14" t="s">
         <v>21</v>
       </c>
-      <c r="AD14" t="s">
+      <c r="AC14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1400,9 +1394,15 @@
         <v>33</v>
       </c>
       <c r="V15" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s">
+        <v>33</v>
+      </c>
+      <c r="W15" t="s">
+        <v>33</v>
+      </c>
+      <c r="X15" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       <c r="R16" t="s">
         <v>21</v>
       </c>
-      <c r="AD16" t="s">
+      <c r="AC16" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       <c r="O17" t="s">
         <v>21</v>
       </c>
-      <c r="AE17" t="s">
+      <c r="AD17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       <c r="Q18" t="s">
         <v>21</v>
       </c>
-      <c r="AE18" t="s">
+      <c r="AD18" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       <c r="S19" t="s">
         <v>21</v>
       </c>
-      <c r="AE19" t="s">
+      <c r="AD19" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="U20" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="V20" t="s">
         <v>14</v>
@@ -1590,12 +1590,9 @@
         <v>14</v>
       </c>
       <c r="Y20" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="s">
+        <v>21</v>
+      </c>
+      <c r="AD20" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1618,6 +1615,9 @@
       <c r="U21" t="s">
         <v>34</v>
       </c>
+      <c r="Y21" t="s">
+        <v>14</v>
+      </c>
       <c r="Z21" t="s">
         <v>14</v>
       </c>
@@ -1625,12 +1625,9 @@
         <v>14</v>
       </c>
       <c r="AB21" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC21" t="s">
-        <v>21</v>
-      </c>
-      <c r="AF21" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE21" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1653,8 +1650,11 @@
       <c r="U22" t="s">
         <v>34</v>
       </c>
+      <c r="AB22" t="s">
+        <v>14</v>
+      </c>
       <c r="AC22" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AD22" t="s">
         <v>33</v>
@@ -1663,9 +1663,6 @@
         <v>33</v>
       </c>
       <c r="AF22" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG22" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1686,15 +1683,12 @@
         <v>9</v>
       </c>
       <c r="U23" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="V23" t="s">
-        <v>14</v>
-      </c>
-      <c r="W23" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG23" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF23" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1715,15 +1709,12 @@
         <v>9</v>
       </c>
       <c r="V24" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="W24" t="s">
-        <v>14</v>
-      </c>
-      <c r="X24" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG24" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF24" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1737,22 +1728,19 @@
       <c r="C25" t="s">
         <v>27</v>
       </c>
+      <c r="W25" t="s">
+        <v>5</v>
+      </c>
       <c r="X25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="s">
-        <v>34</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>21</v>
-      </c>
-      <c r="AG25" t="s">
+        <v>21</v>
+      </c>
+      <c r="AF25" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1766,20 +1754,26 @@
       <c r="C26" t="s">
         <v>28</v>
       </c>
+      <c r="W26" t="s">
+        <v>5</v>
+      </c>
       <c r="X26" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="Z26" t="s">
-        <v>34</v>
+        <v>15</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>15</v>
       </c>
       <c r="AB26" t="s">
         <v>15</v>
       </c>
       <c r="AC26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AD26" t="s">
         <v>14</v>
@@ -1791,7 +1785,7 @@
         <v>14</v>
       </c>
       <c r="AG26" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AH26" t="s">
         <v>22</v>
@@ -1807,13 +1801,13 @@
       <c r="C27" t="s">
         <v>29</v>
       </c>
+      <c r="W27" t="s">
+        <v>5</v>
+      </c>
       <c r="X27" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y27" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z27" t="s">
         <v>34</v>
       </c>
       <c r="AH27" t="s">
@@ -1839,13 +1833,13 @@
       <c r="C28" t="s">
         <v>30</v>
       </c>
+      <c r="W28" t="s">
+        <v>5</v>
+      </c>
       <c r="X28" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y28" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z28" t="s">
         <v>34</v>
       </c>
       <c r="AK28" t="s">
@@ -1858,6 +1852,9 @@
         <v>33</v>
       </c>
       <c r="AN28" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO28" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1871,11 +1868,14 @@
       <c r="C29" t="s">
         <v>31</v>
       </c>
+      <c r="X29" t="s">
+        <v>5</v>
+      </c>
       <c r="Y29" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z29" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="AA29" t="s">
         <v>35</v>
@@ -1884,18 +1884,15 @@
         <v>35</v>
       </c>
       <c r="AC29" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="AD29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AE29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN29" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO29" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1909,22 +1906,22 @@
       <c r="C30" t="s">
         <v>32</v>
       </c>
+      <c r="X30" t="s">
+        <v>5</v>
+      </c>
       <c r="Y30" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD30" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC30" t="s">
         <v>34</v>
       </c>
+      <c r="AE30" t="s">
+        <v>14</v>
+      </c>
       <c r="AF30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG30" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN30" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO30" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1938,19 +1935,19 @@
       <c r="C31" t="s">
         <v>27</v>
       </c>
+      <c r="Y31" t="s">
+        <v>5</v>
+      </c>
       <c r="Z31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AC31" t="s">
+        <v>14</v>
       </c>
       <c r="AD31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO31" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1964,14 +1961,17 @@
       <c r="C32" t="s">
         <v>28</v>
       </c>
+      <c r="Y32" t="s">
+        <v>5</v>
+      </c>
       <c r="Z32" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>34</v>
       </c>
       <c r="AD32" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AE32" t="s">
         <v>15</v>
@@ -1995,9 +1995,15 @@
         <v>14</v>
       </c>
       <c r="AL32" t="s">
-        <v>21</v>
-      </c>
-      <c r="AO32" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM32" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN32" t="s">
+        <v>21</v>
+      </c>
+      <c r="AP32" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2011,25 +2017,25 @@
       <c r="C33" t="s">
         <v>29</v>
       </c>
+      <c r="Y33" t="s">
+        <v>5</v>
+      </c>
       <c r="Z33" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>9</v>
-      </c>
-      <c r="AE33" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD33" t="s">
         <v>34</v>
       </c>
-      <c r="AL33" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM33" t="s">
-        <v>14</v>
-      </c>
       <c r="AN33" t="s">
         <v>14</v>
       </c>
       <c r="AO33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP33" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ33" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2043,28 +2049,49 @@
       <c r="C34" t="s">
         <v>30</v>
       </c>
+      <c r="Y34" t="s">
+        <v>5</v>
+      </c>
       <c r="Z34" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AD34" t="s">
+        <v>16</v>
       </c>
       <c r="AE34" t="s">
         <v>16</v>
       </c>
       <c r="AF34" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG34" t="s">
         <v>34</v>
       </c>
-      <c r="AO34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP34" t="s">
-        <v>33</v>
-      </c>
       <c r="AQ34" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AU34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AX34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY34" t="s">
+        <v>33</v>
+      </c>
+      <c r="AZ34" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2078,22 +2105,19 @@
       <c r="C35" t="s">
         <v>31</v>
       </c>
+      <c r="Z35" t="s">
+        <v>5</v>
+      </c>
       <c r="AA35" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AF35" t="s">
+        <v>14</v>
       </c>
       <c r="AG35" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH35" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI35" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ35" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ35" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2107,22 +2131,22 @@
       <c r="C36" t="s">
         <v>32</v>
       </c>
+      <c r="Z36" t="s">
+        <v>5</v>
+      </c>
       <c r="AA36" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB36" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AF36" t="s">
+        <v>34</v>
       </c>
       <c r="AG36" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ36" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ36" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ36" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2136,28 +2160,25 @@
       <c r="C37" t="s">
         <v>36</v>
       </c>
+      <c r="AH37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>9</v>
+      </c>
       <c r="AJ37" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AK37" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AL37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP37" t="s">
-        <v>21</v>
-      </c>
-      <c r="AQ37" t="s">
+        <v>21</v>
+      </c>
+      <c r="AZ37" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2171,37 +2192,31 @@
       <c r="C38" t="s">
         <v>37</v>
       </c>
+      <c r="AH38" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>9</v>
+      </c>
       <c r="AJ38" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AK38" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL38" t="s">
         <v>34</v>
       </c>
+      <c r="AM38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN38" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO38" t="s">
+        <v>14</v>
+      </c>
       <c r="AP38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AR38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AS38" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT38" t="s">
-        <v>33</v>
-      </c>
-      <c r="AU38" t="s">
-        <v>33</v>
-      </c>
-      <c r="AV38" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW38" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA38" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2215,19 +2230,19 @@
       <c r="C39" t="s">
         <v>38</v>
       </c>
-      <c r="AJ39" t="s">
-        <v>5</v>
+      <c r="AH39" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI39" t="s">
+        <v>9</v>
       </c>
       <c r="AK39" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AL39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM39" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW39" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA39" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2241,16 +2256,16 @@
       <c r="C40" t="s">
         <v>39</v>
       </c>
-      <c r="AJ40" t="s">
-        <v>5</v>
+      <c r="AH40" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK40" t="s">
+        <v>14</v>
       </c>
       <c r="AL40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM40" t="s">
-        <v>21</v>
-      </c>
-      <c r="AW40" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA40" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2264,17 +2279,23 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
+      <c r="AI41" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ41" t="s">
+        <v>9</v>
+      </c>
       <c r="AK41" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AL41" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AM41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO41" t="s">
         <v>14</v>
@@ -2300,7 +2321,7 @@
       <c r="AV41" t="s">
         <v>21</v>
       </c>
-      <c r="AW41" t="s">
+      <c r="BA41" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2314,11 +2335,17 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AK42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL42" t="s">
-        <v>9</v>
+      <c r="AI42" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ42" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM42" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN42" t="s">
+        <v>16</v>
       </c>
       <c r="AO42" t="s">
         <v>16</v>
@@ -2336,6 +2363,9 @@
         <v>14</v>
       </c>
       <c r="AY42" t="s">
+        <v>21</v>
+      </c>
+      <c r="BB42" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2349,10 +2379,10 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AK43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL43" t="s">
+      <c r="AI43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ43" t="s">
         <v>9</v>
       </c>
       <c r="AP43" t="s">
@@ -2384,10 +2414,10 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AK44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL44" t="s">
+      <c r="AI44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ44" t="s">
         <v>9</v>
       </c>
       <c r="AP44" t="s">
@@ -2412,9 +2442,6 @@
         <v>33</v>
       </c>
       <c r="AW44" t="s">
-        <v>33</v>
-      </c>
-      <c r="AX44" t="s">
         <v>21</v>
       </c>
       <c r="BC44" t="s">
@@ -2431,10 +2458,10 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AL45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM45" t="s">
+      <c r="AJ45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" t="s">
         <v>9</v>
       </c>
       <c r="AP45" t="s">
@@ -2462,18 +2489,6 @@
         <v>33</v>
       </c>
       <c r="AX45" t="s">
-        <v>33</v>
-      </c>
-      <c r="AY45" t="s">
-        <v>33</v>
-      </c>
-      <c r="AZ45" t="s">
-        <v>33</v>
-      </c>
-      <c r="BA45" t="s">
-        <v>33</v>
-      </c>
-      <c r="BB45" t="s">
         <v>21</v>
       </c>
       <c r="BC45" t="s">
@@ -2490,10 +2505,10 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AL46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM46" t="s">
+      <c r="AJ46" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" t="s">
         <v>9</v>
       </c>
       <c r="AQ46" t="s">
@@ -2516,10 +2531,10 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="AL47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM47" t="s">
+      <c r="AJ47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" t="s">
         <v>9</v>
       </c>
       <c r="AQ47" t="s">
@@ -2551,14 +2566,14 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
-      <c r="AL48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM48" t="s">
+      <c r="AJ48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" t="s">
         <v>9</v>
       </c>
       <c r="AQ48" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="AR48" t="s">
         <v>14</v>
@@ -2580,10 +2595,10 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-      <c r="AM49" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN49" t="s">
+      <c r="AK49" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO49" t="s">
         <v>9</v>
       </c>
       <c r="AQ49" t="s">
@@ -2612,10 +2627,10 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="AM50" t="s">
-        <v>5</v>
-      </c>
-      <c r="AN50" t="s">
+      <c r="AK50" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO50" t="s">
         <v>9</v>
       </c>
       <c r="AR50" t="s">
@@ -2634,13 +2649,13 @@
         <v>16</v>
       </c>
       <c r="AW50" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="AX50" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AY50" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AZ50" t="s">
         <v>15</v>
@@ -2677,13 +2692,13 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="AM51" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO51" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX51" t="s">
+      <c r="AK51" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP51" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ51" t="s">
         <v>34</v>
       </c>
       <c r="BG51" t="s">
@@ -2709,13 +2724,13 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="AM52" t="s">
-        <v>5</v>
-      </c>
-      <c r="AO52" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX52" t="s">
+      <c r="AK52" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP52" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ52" t="s">
         <v>34</v>
       </c>
       <c r="BJ52" t="s">
@@ -2738,19 +2753,16 @@
       <c r="C53" t="s">
         <v>31</v>
       </c>
-      <c r="AN53" t="s">
-        <v>5</v>
-      </c>
       <c r="AO53" t="s">
-        <v>9</v>
-      </c>
-      <c r="AX53" t="s">
-        <v>34</v>
-      </c>
-      <c r="AY53" t="s">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="AQ53" t="s">
+        <v>9</v>
       </c>
       <c r="AZ53" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA53" t="s">
         <v>21</v>
       </c>
       <c r="BL53" t="s">
@@ -2767,19 +2779,16 @@
       <c r="C54" t="s">
         <v>32</v>
       </c>
-      <c r="AN54" t="s">
-        <v>5</v>
-      </c>
       <c r="AO54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AY54" t="s">
-        <v>34</v>
-      </c>
-      <c r="AZ54" t="s">
-        <v>14</v>
+        <v>5</v>
+      </c>
+      <c r="AQ54" t="s">
+        <v>9</v>
       </c>
       <c r="BA54" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB54" t="s">
         <v>21</v>
       </c>
       <c r="BL54" t="s">
@@ -2796,19 +2805,16 @@
       <c r="C55" t="s">
         <v>27</v>
       </c>
-      <c r="AO55" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ55" t="s">
-        <v>9</v>
-      </c>
-      <c r="AY55" t="s">
-        <v>34</v>
+      <c r="AP55" t="s">
+        <v>5</v>
       </c>
       <c r="AZ55" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA55" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB55" t="s">
         <v>21</v>
       </c>
       <c r="BL55" t="s">
@@ -2825,17 +2831,11 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
-      <c r="AO56" t="s">
-        <v>5</v>
-      </c>
-      <c r="AQ56" t="s">
-        <v>9</v>
-      </c>
-      <c r="AY56" t="s">
-        <v>16</v>
+      <c r="AP56" t="s">
+        <v>5</v>
       </c>
       <c r="AZ56" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA56" t="s">
         <v>16</v>
@@ -2844,7 +2844,7 @@
         <v>16</v>
       </c>
       <c r="BC56" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="BD56" t="s">
         <v>15</v>
@@ -2884,10 +2884,10 @@
       <c r="C57" t="s">
         <v>29</v>
       </c>
-      <c r="AO57" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW57" t="s">
+      <c r="AQ57" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA57" t="s">
         <v>9</v>
       </c>
       <c r="BC57" t="s">
@@ -2903,9 +2903,6 @@
         <v>14</v>
       </c>
       <c r="BN57" t="s">
-        <v>33</v>
-      </c>
-      <c r="BO57" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2919,22 +2916,22 @@
       <c r="C58" t="s">
         <v>30</v>
       </c>
-      <c r="AO58" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW58" t="s">
+      <c r="AQ58" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA58" t="s">
         <v>9</v>
       </c>
       <c r="BC58" t="s">
         <v>34</v>
       </c>
+      <c r="BN58" t="s">
+        <v>14</v>
+      </c>
       <c r="BO58" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BP58" t="s">
-        <v>33</v>
-      </c>
-      <c r="BQ58" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2948,25 +2945,19 @@
       <c r="C59" t="s">
         <v>31</v>
       </c>
-      <c r="AQ59" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW59" t="s">
+      <c r="AZ59" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA59" t="s">
         <v>9</v>
       </c>
       <c r="BC59" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BD59" t="s">
-        <v>14</v>
-      </c>
-      <c r="BE59" t="s">
-        <v>33</v>
-      </c>
-      <c r="BF59" t="s">
-        <v>21</v>
-      </c>
-      <c r="BQ59" t="s">
+        <v>21</v>
+      </c>
+      <c r="BP59" t="s">
         <v>22</v>
       </c>
     </row>
@@ -2980,22 +2971,19 @@
       <c r="C60" t="s">
         <v>32</v>
       </c>
-      <c r="AQ60" t="s">
-        <v>5</v>
-      </c>
-      <c r="AW60" t="s">
+      <c r="AZ60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BA60" t="s">
         <v>9</v>
       </c>
       <c r="BD60" t="s">
-        <v>34</v>
-      </c>
-      <c r="BF60" t="s">
-        <v>14</v>
-      </c>
-      <c r="BG60" t="s">
-        <v>21</v>
-      </c>
-      <c r="BQ60" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE60" t="s">
+        <v>21</v>
+      </c>
+      <c r="BP60" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3009,10 +2997,10 @@
       <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="AW61" t="s">
-        <v>5</v>
-      </c>
-      <c r="AX61" t="s">
+      <c r="BA61" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB61" t="s">
         <v>9</v>
       </c>
       <c r="BD61" t="s">
@@ -3021,7 +3009,7 @@
       <c r="BE61" t="s">
         <v>21</v>
       </c>
-      <c r="BQ61" t="s">
+      <c r="BP61" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3035,10 +3023,10 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="AW62" t="s">
-        <v>5</v>
-      </c>
-      <c r="AY62" t="s">
+      <c r="BA62" t="s">
+        <v>5</v>
+      </c>
+      <c r="BB62" t="s">
         <v>9</v>
       </c>
       <c r="BD62" t="s">
@@ -3051,7 +3039,7 @@
         <v>16</v>
       </c>
       <c r="BG62" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="BH62" t="s">
         <v>15</v>
@@ -3075,12 +3063,9 @@
         <v>14</v>
       </c>
       <c r="BO62" t="s">
-        <v>33</v>
-      </c>
-      <c r="BP62" t="s">
-        <v>21</v>
-      </c>
-      <c r="BR62" t="s">
+        <v>21</v>
+      </c>
+      <c r="BQ62" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3094,7 +3079,7 @@
       <c r="C63" t="s">
         <v>29</v>
       </c>
-      <c r="AW63" t="s">
+      <c r="BA63" t="s">
         <v>5</v>
       </c>
       <c r="BC63" t="s">
@@ -3103,6 +3088,9 @@
       <c r="BG63" t="s">
         <v>34</v>
       </c>
+      <c r="BO63" t="s">
+        <v>14</v>
+      </c>
       <c r="BP63" t="s">
         <v>14</v>
       </c>
@@ -3110,9 +3098,6 @@
         <v>14</v>
       </c>
       <c r="BR63" t="s">
-        <v>14</v>
-      </c>
-      <c r="BS63" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3126,7 +3111,7 @@
       <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="AW64" t="s">
+      <c r="BA64" t="s">
         <v>5</v>
       </c>
       <c r="BC64" t="s">
@@ -3150,13 +3135,13 @@
       <c r="BL64" t="s">
         <v>34</v>
       </c>
+      <c r="BR64" t="s">
+        <v>14</v>
+      </c>
       <c r="BS64" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BT64" t="s">
-        <v>33</v>
-      </c>
-      <c r="BU64" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3170,22 +3155,19 @@
       <c r="C65" t="s">
         <v>31</v>
       </c>
-      <c r="AX65" t="s">
+      <c r="BB65" t="s">
         <v>5</v>
       </c>
       <c r="BC65" t="s">
         <v>9</v>
       </c>
       <c r="BL65" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="BM65" t="s">
-        <v>14</v>
-      </c>
-      <c r="BN65" t="s">
-        <v>21</v>
-      </c>
-      <c r="BU65" t="s">
+        <v>21</v>
+      </c>
+      <c r="BT65" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3199,7 +3181,7 @@
       <c r="C66" t="s">
         <v>32</v>
       </c>
-      <c r="AY66" t="s">
+      <c r="BB66" t="s">
         <v>5</v>
       </c>
       <c r="BC66" t="s">
@@ -3208,13 +3190,13 @@
       <c r="BL66" t="s">
         <v>34</v>
       </c>
+      <c r="BM66" t="s">
+        <v>14</v>
+      </c>
       <c r="BN66" t="s">
-        <v>14</v>
-      </c>
-      <c r="BO66" t="s">
-        <v>21</v>
-      </c>
-      <c r="BU66" t="s">
+        <v>21</v>
+      </c>
+      <c r="BT66" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3228,11 +3210,14 @@
       <c r="C67" t="s">
         <v>36</v>
       </c>
+      <c r="BN67" t="s">
+        <v>5</v>
+      </c>
       <c r="BO67" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BP67" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BQ67" t="s">
         <v>14</v>
@@ -3241,12 +3226,9 @@
         <v>14</v>
       </c>
       <c r="BS67" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BT67" t="s">
-        <v>21</v>
-      </c>
-      <c r="BU67" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3260,15 +3242,18 @@
       <c r="C68" t="s">
         <v>37</v>
       </c>
+      <c r="BN68" t="s">
+        <v>5</v>
+      </c>
       <c r="BO68" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BP68" t="s">
-        <v>9</v>
-      </c>
-      <c r="BQ68" t="s">
         <v>34</v>
       </c>
+      <c r="BS68" t="s">
+        <v>14</v>
+      </c>
       <c r="BT68" t="s">
         <v>14</v>
       </c>
@@ -3276,7 +3261,7 @@
         <v>14</v>
       </c>
       <c r="BV68" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BW68" t="s">
         <v>33</v>
@@ -3285,9 +3270,6 @@
         <v>33</v>
       </c>
       <c r="BY68" t="s">
-        <v>33</v>
-      </c>
-      <c r="BZ68" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3301,19 +3283,19 @@
       <c r="C69" t="s">
         <v>38</v>
       </c>
+      <c r="BN69" t="s">
+        <v>5</v>
+      </c>
       <c r="BO69" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BP69" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BQ69" t="s">
-        <v>14</v>
-      </c>
-      <c r="BR69" t="s">
-        <v>21</v>
-      </c>
-      <c r="BZ69" t="s">
+        <v>21</v>
+      </c>
+      <c r="BY69" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3327,19 +3309,19 @@
       <c r="C70" t="s">
         <v>39</v>
       </c>
+      <c r="BN70" t="s">
+        <v>5</v>
+      </c>
       <c r="BO70" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BP70" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BQ70" t="s">
-        <v>14</v>
-      </c>
-      <c r="BR70" t="s">
-        <v>21</v>
-      </c>
-      <c r="BZ70" t="s">
+        <v>21</v>
+      </c>
+      <c r="BY70" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3353,14 +3335,17 @@
       <c r="C71" t="s">
         <v>18</v>
       </c>
+      <c r="BO71" t="s">
+        <v>5</v>
+      </c>
       <c r="BP71" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BQ71" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BR71" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BS71" t="s">
         <v>14</v>
@@ -3369,7 +3354,7 @@
         <v>14</v>
       </c>
       <c r="BU71" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BV71" t="s">
         <v>33</v>
@@ -3384,9 +3369,6 @@
         <v>33</v>
       </c>
       <c r="BZ71" t="s">
-        <v>33</v>
-      </c>
-      <c r="CA71" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3400,18 +3382,21 @@
       <c r="C72" t="s">
         <v>19</v>
       </c>
+      <c r="BO72" t="s">
+        <v>5</v>
+      </c>
       <c r="BP72" t="s">
-        <v>5</v>
-      </c>
-      <c r="BQ72" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BR72" t="s">
+        <v>16</v>
       </c>
       <c r="BS72" t="s">
-        <v>16</v>
-      </c>
-      <c r="BT72" t="s">
         <v>34</v>
       </c>
+      <c r="BZ72" t="s">
+        <v>14</v>
+      </c>
       <c r="CA72" t="s">
         <v>14</v>
       </c>
@@ -3419,15 +3404,9 @@
         <v>14</v>
       </c>
       <c r="CC72" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CD72" t="s">
-        <v>33</v>
-      </c>
-      <c r="CE72" t="s">
-        <v>33</v>
-      </c>
-      <c r="CF72" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3441,17 +3420,23 @@
       <c r="C73" t="s">
         <v>20</v>
       </c>
+      <c r="BO73" t="s">
+        <v>5</v>
+      </c>
       <c r="BP73" t="s">
-        <v>5</v>
-      </c>
-      <c r="BQ73" t="s">
-        <v>9</v>
-      </c>
-      <c r="BT73" t="s">
+        <v>9</v>
+      </c>
+      <c r="BS73" t="s">
         <v>34</v>
       </c>
+      <c r="CD73" t="s">
+        <v>15</v>
+      </c>
+      <c r="CE73" t="s">
+        <v>14</v>
+      </c>
       <c r="CF73" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CG73" t="s">
         <v>14</v>
@@ -3460,12 +3445,6 @@
         <v>14</v>
       </c>
       <c r="CI73" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ73" t="s">
-        <v>14</v>
-      </c>
-      <c r="CK73" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3479,11 +3458,14 @@
       <c r="C74" t="s">
         <v>23</v>
       </c>
+      <c r="BO74" t="s">
+        <v>5</v>
+      </c>
       <c r="BP74" t="s">
-        <v>5</v>
-      </c>
-      <c r="BQ74" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BS74" t="s">
+        <v>14</v>
       </c>
       <c r="BT74" t="s">
         <v>14</v>
@@ -3495,7 +3477,7 @@
         <v>14</v>
       </c>
       <c r="BW74" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BX74" t="s">
         <v>33</v>
@@ -3507,12 +3489,9 @@
         <v>33</v>
       </c>
       <c r="CA74" t="s">
-        <v>33</v>
-      </c>
-      <c r="CB74" t="s">
-        <v>21</v>
-      </c>
-      <c r="CK74" t="s">
+        <v>21</v>
+      </c>
+      <c r="CI74" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3526,11 +3505,14 @@
       <c r="C75" t="s">
         <v>24</v>
       </c>
+      <c r="BP75" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ75" t="s">
-        <v>5</v>
-      </c>
-      <c r="BR75" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BS75" t="s">
+        <v>14</v>
       </c>
       <c r="BT75" t="s">
         <v>14</v>
@@ -3548,7 +3530,7 @@
         <v>14</v>
       </c>
       <c r="BY75" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BZ75" t="s">
         <v>33</v>
@@ -3560,9 +3542,18 @@
         <v>33</v>
       </c>
       <c r="CC75" t="s">
-        <v>21</v>
-      </c>
-      <c r="CK75" t="s">
+        <v>33</v>
+      </c>
+      <c r="CD75" t="s">
+        <v>33</v>
+      </c>
+      <c r="CE75" t="s">
+        <v>33</v>
+      </c>
+      <c r="CF75" t="s">
+        <v>21</v>
+      </c>
+      <c r="CI75" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3576,19 +3567,22 @@
       <c r="C76" t="s">
         <v>25</v>
       </c>
+      <c r="BP76" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ76" t="s">
-        <v>5</v>
-      </c>
-      <c r="BR76" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BT76" t="s">
+        <v>14</v>
       </c>
       <c r="BU76" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BV76" t="s">
         <v>21</v>
       </c>
-      <c r="CK76" t="s">
+      <c r="CI76" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3602,28 +3596,28 @@
       <c r="C77" t="s">
         <v>13</v>
       </c>
+      <c r="BP77" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ77" t="s">
-        <v>5</v>
-      </c>
-      <c r="BR77" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BT77" t="s">
+        <v>15</v>
       </c>
       <c r="BU77" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BV77" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="BW77" t="s">
         <v>33</v>
       </c>
       <c r="BX77" t="s">
-        <v>33</v>
-      </c>
-      <c r="BY77" t="s">
-        <v>21</v>
-      </c>
-      <c r="CL77" t="s">
+        <v>21</v>
+      </c>
+      <c r="CJ77" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3637,22 +3631,19 @@
       <c r="C78" t="s">
         <v>26</v>
       </c>
+      <c r="BP78" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ78" t="s">
-        <v>5</v>
-      </c>
-      <c r="BR78" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BT78" t="s">
+        <v>14</v>
       </c>
       <c r="BU78" t="s">
-        <v>34</v>
-      </c>
-      <c r="BV78" t="s">
-        <v>14</v>
-      </c>
-      <c r="BW78" t="s">
-        <v>21</v>
-      </c>
-      <c r="CL78" t="s">
+        <v>21</v>
+      </c>
+      <c r="CJ78" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3666,25 +3657,22 @@
       <c r="C79" t="s">
         <v>27</v>
       </c>
+      <c r="BQ79" t="s">
+        <v>5</v>
+      </c>
       <c r="BR79" t="s">
-        <v>5</v>
-      </c>
-      <c r="BS79" t="s">
-        <v>9</v>
-      </c>
-      <c r="BU79" t="s">
+        <v>9</v>
+      </c>
+      <c r="BT79" t="s">
         <v>34</v>
       </c>
       <c r="BV79" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BW79" t="s">
-        <v>14</v>
-      </c>
-      <c r="BX79" t="s">
-        <v>21</v>
-      </c>
-      <c r="CL79" t="s">
+        <v>21</v>
+      </c>
+      <c r="CJ79" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3698,11 +3686,14 @@
       <c r="C80" t="s">
         <v>28</v>
       </c>
+      <c r="BQ80" t="s">
+        <v>5</v>
+      </c>
       <c r="BR80" t="s">
-        <v>5</v>
-      </c>
-      <c r="BS80" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="BU80" t="s">
+        <v>16</v>
       </c>
       <c r="BV80" t="s">
         <v>16</v>
@@ -3720,10 +3711,10 @@
         <v>16</v>
       </c>
       <c r="CA80" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CB80" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="CC80" t="s">
         <v>14</v>
@@ -3732,15 +3723,9 @@
         <v>14</v>
       </c>
       <c r="CE80" t="s">
-        <v>14</v>
-      </c>
-      <c r="CF80" t="s">
-        <v>14</v>
-      </c>
-      <c r="CG80" t="s">
-        <v>21</v>
-      </c>
-      <c r="CL80" t="s">
+        <v>21</v>
+      </c>
+      <c r="CJ80" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3754,28 +3739,28 @@
       <c r="C81" t="s">
         <v>29</v>
       </c>
+      <c r="BQ81" t="s">
+        <v>5</v>
+      </c>
       <c r="BR81" t="s">
-        <v>5</v>
-      </c>
-      <c r="BS81" t="s">
-        <v>9</v>
-      </c>
-      <c r="CB81" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA81" t="s">
         <v>34</v>
       </c>
+      <c r="CE81" t="s">
+        <v>14</v>
+      </c>
+      <c r="CF81" t="s">
+        <v>14</v>
+      </c>
       <c r="CG81" t="s">
         <v>14</v>
       </c>
       <c r="CH81" t="s">
-        <v>14</v>
-      </c>
-      <c r="CI81" t="s">
-        <v>14</v>
-      </c>
-      <c r="CJ81" t="s">
-        <v>21</v>
-      </c>
-      <c r="CM81" t="s">
+        <v>21</v>
+      </c>
+      <c r="CK81" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3789,28 +3774,28 @@
       <c r="C82" t="s">
         <v>30</v>
       </c>
+      <c r="BQ82" t="s">
+        <v>5</v>
+      </c>
       <c r="BR82" t="s">
-        <v>5</v>
-      </c>
-      <c r="BS82" t="s">
-        <v>9</v>
-      </c>
-      <c r="CB82" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA82" t="s">
         <v>34</v>
       </c>
+      <c r="CH82" t="s">
+        <v>14</v>
+      </c>
+      <c r="CI82" t="s">
+        <v>33</v>
+      </c>
       <c r="CJ82" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CK82" t="s">
         <v>33</v>
       </c>
       <c r="CL82" t="s">
-        <v>33</v>
-      </c>
-      <c r="CM82" t="s">
-        <v>33</v>
-      </c>
-      <c r="CN82" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3824,22 +3809,19 @@
       <c r="C83" t="s">
         <v>31</v>
       </c>
+      <c r="BR83" t="s">
+        <v>5</v>
+      </c>
       <c r="BS83" t="s">
-        <v>5</v>
-      </c>
-      <c r="BT83" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="CA83" t="s">
+        <v>14</v>
       </c>
       <c r="CB83" t="s">
-        <v>34</v>
-      </c>
-      <c r="CC83" t="s">
-        <v>14</v>
-      </c>
-      <c r="CD83" t="s">
-        <v>21</v>
-      </c>
-      <c r="CN83" t="s">
+        <v>21</v>
+      </c>
+      <c r="CL83" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3853,22 +3835,19 @@
       <c r="C84" t="s">
         <v>32</v>
       </c>
+      <c r="BR84" t="s">
+        <v>5</v>
+      </c>
       <c r="BS84" t="s">
-        <v>5</v>
-      </c>
-      <c r="BT84" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="CB84" t="s">
+        <v>14</v>
       </c>
       <c r="CC84" t="s">
-        <v>34</v>
-      </c>
-      <c r="CD84" t="s">
-        <v>14</v>
-      </c>
-      <c r="CE84" t="s">
-        <v>21</v>
-      </c>
-      <c r="CN84" t="s">
+        <v>21</v>
+      </c>
+      <c r="CL84" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3882,22 +3861,19 @@
       <c r="C85" t="s">
         <v>27</v>
       </c>
+      <c r="BS85" t="s">
+        <v>5</v>
+      </c>
       <c r="BT85" t="s">
-        <v>5</v>
-      </c>
-      <c r="BU85" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="CB85" t="s">
+        <v>14</v>
       </c>
       <c r="CC85" t="s">
-        <v>34</v>
-      </c>
-      <c r="CD85" t="s">
-        <v>14</v>
-      </c>
-      <c r="CE85" t="s">
-        <v>21</v>
-      </c>
-      <c r="CN85" t="s">
+        <v>21</v>
+      </c>
+      <c r="CL85" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3911,11 +3887,14 @@
       <c r="C86" t="s">
         <v>28</v>
       </c>
+      <c r="BS86" t="s">
+        <v>5</v>
+      </c>
       <c r="BT86" t="s">
-        <v>5</v>
-      </c>
-      <c r="BU86" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="CB86" t="s">
+        <v>16</v>
       </c>
       <c r="CC86" t="s">
         <v>16</v>
@@ -3924,22 +3903,22 @@
         <v>16</v>
       </c>
       <c r="CE86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CF86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CG86" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="CH86" t="s">
         <v>15</v>
       </c>
       <c r="CI86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CJ86" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CK86" t="s">
         <v>14</v>
@@ -3948,12 +3927,9 @@
         <v>14</v>
       </c>
       <c r="CM86" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CN86" t="s">
-        <v>14</v>
-      </c>
-      <c r="CO86" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3967,15 +3943,18 @@
       <c r="C87" t="s">
         <v>29</v>
       </c>
-      <c r="BT87" t="s">
-        <v>5</v>
-      </c>
-      <c r="BZ87" t="s">
-        <v>9</v>
-      </c>
-      <c r="CG87" t="s">
+      <c r="BS87" t="s">
+        <v>5</v>
+      </c>
+      <c r="BY87" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE87" t="s">
         <v>34</v>
       </c>
+      <c r="CN87" t="s">
+        <v>14</v>
+      </c>
       <c r="CO87" t="s">
         <v>14</v>
       </c>
@@ -3983,9 +3962,6 @@
         <v>14</v>
       </c>
       <c r="CQ87" t="s">
-        <v>14</v>
-      </c>
-      <c r="CR87" t="s">
         <v>22</v>
       </c>
     </row>
@@ -3999,17 +3975,20 @@
       <c r="C88" t="s">
         <v>30</v>
       </c>
-      <c r="BT88" t="s">
-        <v>5</v>
-      </c>
-      <c r="BZ88" t="s">
-        <v>9</v>
-      </c>
-      <c r="CG88" t="s">
+      <c r="BS88" t="s">
+        <v>5</v>
+      </c>
+      <c r="BY88" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE88" t="s">
         <v>34</v>
       </c>
+      <c r="CQ88" t="s">
+        <v>14</v>
+      </c>
       <c r="CR88" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CS88" t="s">
         <v>33</v>
@@ -4031,11 +4010,17 @@
       <c r="C89" t="s">
         <v>31</v>
       </c>
-      <c r="BU89" t="s">
-        <v>5</v>
-      </c>
-      <c r="BZ89" t="s">
-        <v>9</v>
+      <c r="BT89" t="s">
+        <v>5</v>
+      </c>
+      <c r="BY89" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE89" t="s">
+        <v>35</v>
+      </c>
+      <c r="CF89" t="s">
+        <v>35</v>
       </c>
       <c r="CG89" t="s">
         <v>35</v>
@@ -4044,18 +4029,12 @@
         <v>35</v>
       </c>
       <c r="CI89" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="CJ89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="CK89" t="s">
-        <v>34</v>
-      </c>
-      <c r="CL89" t="s">
-        <v>14</v>
-      </c>
-      <c r="CM89" t="s">
         <v>21</v>
       </c>
       <c r="CU89" t="s">
@@ -4072,19 +4051,19 @@
       <c r="C90" t="s">
         <v>32</v>
       </c>
-      <c r="BU90" t="s">
-        <v>5</v>
-      </c>
-      <c r="BZ90" t="s">
-        <v>9</v>
+      <c r="BT90" t="s">
+        <v>5</v>
+      </c>
+      <c r="BY90" t="s">
+        <v>9</v>
+      </c>
+      <c r="CI90" t="s">
+        <v>34</v>
       </c>
       <c r="CK90" t="s">
-        <v>34</v>
-      </c>
-      <c r="CM90" t="s">
-        <v>14</v>
-      </c>
-      <c r="CN90" t="s">
+        <v>14</v>
+      </c>
+      <c r="CL90" t="s">
         <v>21</v>
       </c>
       <c r="CU90" t="s">
@@ -4101,16 +4080,16 @@
       <c r="C91" t="s">
         <v>27</v>
       </c>
+      <c r="BY91" t="s">
+        <v>5</v>
+      </c>
       <c r="BZ91" t="s">
-        <v>5</v>
-      </c>
-      <c r="CA91" t="s">
-        <v>9</v>
-      </c>
-      <c r="CK91" t="s">
-        <v>14</v>
-      </c>
-      <c r="CL91" t="s">
+        <v>9</v>
+      </c>
+      <c r="CI91" t="s">
+        <v>14</v>
+      </c>
+      <c r="CJ91" t="s">
         <v>21</v>
       </c>
       <c r="CU91" t="s">
@@ -4127,14 +4106,20 @@
       <c r="C92" t="s">
         <v>28</v>
       </c>
-      <c r="BZ92" t="s">
-        <v>5</v>
-      </c>
-      <c r="CF92" t="s">
-        <v>9</v>
+      <c r="BY92" t="s">
+        <v>5</v>
+      </c>
+      <c r="CD92" t="s">
+        <v>9</v>
+      </c>
+      <c r="CI92" t="s">
+        <v>34</v>
+      </c>
+      <c r="CJ92" t="s">
+        <v>15</v>
       </c>
       <c r="CK92" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="CL92" t="s">
         <v>15</v>
@@ -4143,7 +4128,7 @@
         <v>15</v>
       </c>
       <c r="CN92" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CO92" t="s">
         <v>14</v>
@@ -4155,9 +4140,12 @@
         <v>14</v>
       </c>
       <c r="CR92" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="CS92" t="s">
+        <v>33</v>
+      </c>
+      <c r="CT92" t="s">
         <v>21</v>
       </c>
       <c r="CV92" t="s">
@@ -4174,18 +4162,15 @@
       <c r="C93" t="s">
         <v>29</v>
       </c>
-      <c r="BZ93" t="s">
-        <v>5</v>
-      </c>
-      <c r="CK93" t="s">
-        <v>9</v>
-      </c>
-      <c r="CL93" t="s">
+      <c r="BY93" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI93" t="s">
+        <v>9</v>
+      </c>
+      <c r="CJ93" t="s">
         <v>34</v>
       </c>
-      <c r="CS93" t="s">
-        <v>14</v>
-      </c>
       <c r="CT93" t="s">
         <v>14</v>
       </c>
@@ -4193,6 +4178,9 @@
         <v>14</v>
       </c>
       <c r="CV93" t="s">
+        <v>14</v>
+      </c>
+      <c r="CW93" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4206,26 +4194,23 @@
       <c r="C94" t="s">
         <v>30</v>
       </c>
-      <c r="BZ94" t="s">
-        <v>5</v>
+      <c r="BY94" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI94" t="s">
+        <v>9</v>
+      </c>
+      <c r="CJ94" t="s">
+        <v>16</v>
       </c>
       <c r="CK94" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="CL94" t="s">
-        <v>16</v>
-      </c>
-      <c r="CM94" t="s">
-        <v>16</v>
-      </c>
-      <c r="CN94" t="s">
         <v>34</v>
       </c>
-      <c r="CV94" t="s">
-        <v>14</v>
-      </c>
       <c r="CW94" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="CX94" t="s">
         <v>22</v>
@@ -4241,19 +4226,16 @@
       <c r="C95" t="s">
         <v>31</v>
       </c>
-      <c r="CA95" t="s">
-        <v>5</v>
-      </c>
-      <c r="CK95" t="s">
-        <v>9</v>
-      </c>
-      <c r="CN95" t="s">
-        <v>34</v>
-      </c>
-      <c r="CO95" t="s">
-        <v>14</v>
-      </c>
-      <c r="CP95" t="s">
+      <c r="BZ95" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI95" t="s">
+        <v>9</v>
+      </c>
+      <c r="CL95" t="s">
+        <v>14</v>
+      </c>
+      <c r="CM95" t="s">
         <v>21</v>
       </c>
       <c r="CX95" t="s">
@@ -4270,19 +4252,19 @@
       <c r="C96" t="s">
         <v>32</v>
       </c>
-      <c r="CF96" t="s">
-        <v>5</v>
-      </c>
-      <c r="CK96" t="s">
-        <v>9</v>
+      <c r="CD96" t="s">
+        <v>5</v>
+      </c>
+      <c r="CI96" t="s">
+        <v>9</v>
+      </c>
+      <c r="CL96" t="s">
+        <v>34</v>
+      </c>
+      <c r="CM96" t="s">
+        <v>14</v>
       </c>
       <c r="CN96" t="s">
-        <v>34</v>
-      </c>
-      <c r="CP96" t="s">
-        <v>14</v>
-      </c>
-      <c r="CQ96" t="s">
         <v>21</v>
       </c>
       <c r="CX96" t="s">
@@ -4299,25 +4281,22 @@
       <c r="C97" t="s">
         <v>36</v>
       </c>
+      <c r="CN97" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO97" t="s">
+        <v>9</v>
+      </c>
+      <c r="CP97" t="s">
+        <v>14</v>
+      </c>
       <c r="CQ97" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CR97" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CS97" t="s">
-        <v>15</v>
-      </c>
-      <c r="CT97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CU97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CV97" t="s">
-        <v>14</v>
-      </c>
-      <c r="CW97" t="s">
         <v>21</v>
       </c>
       <c r="CX97" t="s">
@@ -4334,25 +4313,31 @@
       <c r="C98" t="s">
         <v>37</v>
       </c>
+      <c r="CN98" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO98" t="s">
+        <v>9</v>
+      </c>
+      <c r="CP98" t="s">
+        <v>16</v>
+      </c>
       <c r="CQ98" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR98" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="CS98" t="s">
-        <v>34</v>
-      </c>
-      <c r="CW98" t="s">
-        <v>14</v>
-      </c>
-      <c r="CX98" t="s">
-        <v>14</v>
+        <v>14</v>
+      </c>
+      <c r="CT98" t="s">
+        <v>14</v>
+      </c>
+      <c r="CU98" t="s">
+        <v>14</v>
+      </c>
+      <c r="CV98" t="s">
+        <v>21</v>
       </c>
       <c r="CY98" t="s">
-        <v>14</v>
-      </c>
-      <c r="CZ98" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4366,19 +4351,19 @@
       <c r="C99" t="s">
         <v>38</v>
       </c>
+      <c r="CN99" t="s">
+        <v>5</v>
+      </c>
+      <c r="CO99" t="s">
+        <v>9</v>
+      </c>
       <c r="CQ99" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="CR99" t="s">
-        <v>9</v>
-      </c>
-      <c r="CS99" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT99" t="s">
-        <v>21</v>
-      </c>
-      <c r="CZ99" t="s">
+        <v>21</v>
+      </c>
+      <c r="CY99" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4392,16 +4377,16 @@
       <c r="C100" t="s">
         <v>39</v>
       </c>
+      <c r="CN100" t="s">
+        <v>5</v>
+      </c>
       <c r="CQ100" t="s">
-        <v>5</v>
-      </c>
-      <c r="CS100" t="s">
-        <v>14</v>
-      </c>
-      <c r="CT100" t="s">
-        <v>21</v>
-      </c>
-      <c r="CZ100" t="s">
+        <v>14</v>
+      </c>
+      <c r="CR100" t="s">
+        <v>21</v>
+      </c>
+      <c r="CY100" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4415,11 +4400,20 @@
       <c r="C101" t="s">
         <v>40</v>
       </c>
+      <c r="CO101" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP101" t="s">
+        <v>9</v>
+      </c>
+      <c r="CQ101" t="s">
+        <v>16</v>
+      </c>
       <c r="CR101" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="CS101" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="CT101" t="s">
         <v>16</v>
@@ -4461,9 +4455,6 @@
         <v>33</v>
       </c>
       <c r="DG101" t="s">
-        <v>33</v>
-      </c>
-      <c r="DH101" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4477,10 +4468,10 @@
       <c r="C102" t="s">
         <v>41</v>
       </c>
-      <c r="CR102" t="s">
-        <v>5</v>
-      </c>
-      <c r="CS102" t="s">
+      <c r="CO102" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP102" t="s">
         <v>9</v>
       </c>
       <c r="CU102" t="s">
@@ -4498,7 +4489,7 @@
       <c r="CY102" t="s">
         <v>21</v>
       </c>
-      <c r="DH102" t="s">
+      <c r="DG102" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4512,10 +4503,10 @@
       <c r="C103" t="s">
         <v>42</v>
       </c>
-      <c r="CR103" t="s">
-        <v>5</v>
-      </c>
-      <c r="CS103" t="s">
+      <c r="CO103" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP103" t="s">
         <v>9</v>
       </c>
       <c r="CX103" t="s">
@@ -4525,12 +4516,9 @@
         <v>14</v>
       </c>
       <c r="CZ103" t="s">
-        <v>33</v>
-      </c>
-      <c r="DA103" t="s">
-        <v>21</v>
-      </c>
-      <c r="DH103" t="s">
+        <v>21</v>
+      </c>
+      <c r="DG103" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4544,25 +4532,22 @@
       <c r="C104" t="s">
         <v>43</v>
       </c>
-      <c r="CR104" t="s">
-        <v>5</v>
-      </c>
-      <c r="CS104" t="s">
+      <c r="CO104" t="s">
+        <v>5</v>
+      </c>
+      <c r="CP104" t="s">
         <v>9</v>
       </c>
       <c r="CY104" t="s">
         <v>16</v>
       </c>
       <c r="CZ104" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="DA104" t="s">
-        <v>14</v>
-      </c>
-      <c r="DB104" t="s">
-        <v>21</v>
-      </c>
-      <c r="DH104" t="s">
+        <v>21</v>
+      </c>
+      <c r="DG104" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4576,22 +4561,22 @@
       <c r="C105" t="s">
         <v>44</v>
       </c>
-      <c r="CS105" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT105" t="s">
-        <v>9</v>
+      <c r="CP105" t="s">
+        <v>5</v>
+      </c>
+      <c r="CQ105" t="s">
+        <v>9</v>
+      </c>
+      <c r="CZ105" t="s">
+        <v>16</v>
       </c>
       <c r="DA105" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="DB105" t="s">
-        <v>14</v>
-      </c>
-      <c r="DC105" t="s">
-        <v>21</v>
-      </c>
-      <c r="DI105" t="s">
+        <v>21</v>
+      </c>
+      <c r="DH105" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4605,22 +4590,22 @@
       <c r="C106" t="s">
         <v>45</v>
       </c>
-      <c r="CS106" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT106" t="s">
-        <v>9</v>
+      <c r="CP106" t="s">
+        <v>5</v>
+      </c>
+      <c r="CQ106" t="s">
+        <v>9</v>
+      </c>
+      <c r="DA106" t="s">
+        <v>16</v>
       </c>
       <c r="DB106" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="DC106" t="s">
-        <v>14</v>
-      </c>
-      <c r="DD106" t="s">
-        <v>21</v>
-      </c>
-      <c r="DI106" t="s">
+        <v>21</v>
+      </c>
+      <c r="DH106" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4634,22 +4619,22 @@
       <c r="C107" t="s">
         <v>46</v>
       </c>
-      <c r="CS107" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT107" t="s">
-        <v>9</v>
+      <c r="CP107" t="s">
+        <v>5</v>
+      </c>
+      <c r="CQ107" t="s">
+        <v>9</v>
+      </c>
+      <c r="DB107" t="s">
+        <v>16</v>
       </c>
       <c r="DC107" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="DD107" t="s">
-        <v>14</v>
-      </c>
-      <c r="DE107" t="s">
-        <v>21</v>
-      </c>
-      <c r="DI107" t="s">
+        <v>21</v>
+      </c>
+      <c r="DH107" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4663,22 +4648,22 @@
       <c r="C108" t="s">
         <v>47</v>
       </c>
-      <c r="CS108" t="s">
-        <v>5</v>
-      </c>
-      <c r="CT108" t="s">
-        <v>9</v>
+      <c r="CP108" t="s">
+        <v>5</v>
+      </c>
+      <c r="CQ108" t="s">
+        <v>9</v>
+      </c>
+      <c r="DC108" t="s">
+        <v>16</v>
       </c>
       <c r="DD108" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="DE108" t="s">
-        <v>14</v>
-      </c>
-      <c r="DF108" t="s">
-        <v>21</v>
-      </c>
-      <c r="DI108" t="s">
+        <v>21</v>
+      </c>
+      <c r="DH108" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4692,22 +4677,22 @@
       <c r="C109" t="s">
         <v>48</v>
       </c>
-      <c r="CT109" t="s">
-        <v>5</v>
-      </c>
-      <c r="CU109" t="s">
-        <v>9</v>
+      <c r="CQ109" t="s">
+        <v>5</v>
+      </c>
+      <c r="CR109" t="s">
+        <v>9</v>
+      </c>
+      <c r="DD109" t="s">
+        <v>16</v>
       </c>
       <c r="DE109" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="DF109" t="s">
-        <v>14</v>
-      </c>
-      <c r="DG109" t="s">
-        <v>21</v>
-      </c>
-      <c r="DJ109" t="s">
+        <v>21</v>
+      </c>
+      <c r="DI109" t="s">
         <v>22</v>
       </c>
     </row>

--- a/project/outputs_xlsx_solution/test33.4-wide-NB-1.xlsx
+++ b/project/outputs_xlsx_solution/test33.4-wide-NB-1.xlsx
@@ -2259,6 +2259,9 @@
       <c r="AH40" t="s">
         <v>5</v>
       </c>
+      <c r="AI40" t="s">
+        <v>9</v>
+      </c>
       <c r="AK40" t="s">
         <v>14</v>
       </c>
@@ -2279,20 +2282,11 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
-      <c r="AI41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ41" t="s">
-        <v>9</v>
-      </c>
-      <c r="AK41" t="s">
-        <v>16</v>
-      </c>
       <c r="AL41" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AM41" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AN41" t="s">
         <v>15</v>
@@ -2335,14 +2329,11 @@
       <c r="C42" t="s">
         <v>19</v>
       </c>
-      <c r="AI42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ42" t="s">
-        <v>9</v>
+      <c r="AL42" t="s">
+        <v>5</v>
       </c>
       <c r="AM42" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AN42" t="s">
         <v>16</v>
@@ -2379,10 +2370,10 @@
       <c r="C43" t="s">
         <v>20</v>
       </c>
-      <c r="AI43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ43" t="s">
+      <c r="AL43" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM43" t="s">
         <v>9</v>
       </c>
       <c r="AP43" t="s">
@@ -2414,10 +2405,10 @@
       <c r="C44" t="s">
         <v>23</v>
       </c>
-      <c r="AI44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ44" t="s">
+      <c r="AL44" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM44" t="s">
         <v>9</v>
       </c>
       <c r="AP44" t="s">
@@ -2458,10 +2449,10 @@
       <c r="C45" t="s">
         <v>24</v>
       </c>
-      <c r="AJ45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK45" t="s">
+      <c r="AM45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN45" t="s">
         <v>9</v>
       </c>
       <c r="AP45" t="s">
@@ -2505,10 +2496,10 @@
       <c r="C46" t="s">
         <v>25</v>
       </c>
-      <c r="AJ46" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK46" t="s">
+      <c r="AM46" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN46" t="s">
         <v>9</v>
       </c>
       <c r="AQ46" t="s">
@@ -2531,10 +2522,10 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
-      <c r="AJ47" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK47" t="s">
+      <c r="AM47" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN47" t="s">
         <v>9</v>
       </c>
       <c r="AQ47" t="s">
@@ -2566,10 +2557,10 @@
       <c r="C48" t="s">
         <v>26</v>
       </c>
-      <c r="AJ48" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK48" t="s">
+      <c r="AM48" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN48" t="s">
         <v>9</v>
       </c>
       <c r="AQ48" t="s">
@@ -2595,7 +2586,7 @@
       <c r="C49" t="s">
         <v>27</v>
       </c>
-      <c r="AK49" t="s">
+      <c r="AN49" t="s">
         <v>5</v>
       </c>
       <c r="AO49" t="s">
@@ -2627,7 +2618,7 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="AK50" t="s">
+      <c r="AN50" t="s">
         <v>5</v>
       </c>
       <c r="AO50" t="s">
@@ -2692,7 +2683,7 @@
       <c r="C51" t="s">
         <v>29</v>
       </c>
-      <c r="AK51" t="s">
+      <c r="AN51" t="s">
         <v>5</v>
       </c>
       <c r="AP51" t="s">
@@ -2724,7 +2715,7 @@
       <c r="C52" t="s">
         <v>30</v>
       </c>
-      <c r="AK52" t="s">
+      <c r="AN52" t="s">
         <v>5</v>
       </c>
       <c r="AP52" t="s">
@@ -4380,6 +4371,9 @@
       <c r="CN100" t="s">
         <v>5</v>
       </c>
+      <c r="CO100" t="s">
+        <v>9</v>
+      </c>
       <c r="CQ100" t="s">
         <v>14</v>
       </c>
@@ -4400,20 +4394,11 @@
       <c r="C101" t="s">
         <v>40</v>
       </c>
-      <c r="CO101" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP101" t="s">
-        <v>9</v>
-      </c>
-      <c r="CQ101" t="s">
-        <v>16</v>
-      </c>
       <c r="CR101" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="CS101" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="CT101" t="s">
         <v>16</v>
@@ -4468,10 +4453,10 @@
       <c r="C102" t="s">
         <v>41</v>
       </c>
-      <c r="CO102" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP102" t="s">
+      <c r="CR102" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS102" t="s">
         <v>9</v>
       </c>
       <c r="CU102" t="s">
@@ -4503,10 +4488,10 @@
       <c r="C103" t="s">
         <v>42</v>
       </c>
-      <c r="CO103" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP103" t="s">
+      <c r="CR103" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS103" t="s">
         <v>9</v>
       </c>
       <c r="CX103" t="s">
@@ -4532,10 +4517,10 @@
       <c r="C104" t="s">
         <v>43</v>
       </c>
-      <c r="CO104" t="s">
-        <v>5</v>
-      </c>
-      <c r="CP104" t="s">
+      <c r="CR104" t="s">
+        <v>5</v>
+      </c>
+      <c r="CS104" t="s">
         <v>9</v>
       </c>
       <c r="CY104" t="s">
@@ -4561,10 +4546,10 @@
       <c r="C105" t="s">
         <v>44</v>
       </c>
-      <c r="CP105" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ105" t="s">
+      <c r="CS105" t="s">
+        <v>5</v>
+      </c>
+      <c r="CT105" t="s">
         <v>9</v>
       </c>
       <c r="CZ105" t="s">
@@ -4590,10 +4575,10 @@
       <c r="C106" t="s">
         <v>45</v>
       </c>
-      <c r="CP106" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ106" t="s">
+      <c r="CS106" t="s">
+        <v>5</v>
+      </c>
+      <c r="CT106" t="s">
         <v>9</v>
       </c>
       <c r="DA106" t="s">
@@ -4619,10 +4604,10 @@
       <c r="C107" t="s">
         <v>46</v>
       </c>
-      <c r="CP107" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ107" t="s">
+      <c r="CS107" t="s">
+        <v>5</v>
+      </c>
+      <c r="CT107" t="s">
         <v>9</v>
       </c>
       <c r="DB107" t="s">
@@ -4648,10 +4633,10 @@
       <c r="C108" t="s">
         <v>47</v>
       </c>
-      <c r="CP108" t="s">
-        <v>5</v>
-      </c>
-      <c r="CQ108" t="s">
+      <c r="CS108" t="s">
+        <v>5</v>
+      </c>
+      <c r="CT108" t="s">
         <v>9</v>
       </c>
       <c r="DC108" t="s">
@@ -4677,10 +4662,10 @@
       <c r="C109" t="s">
         <v>48</v>
       </c>
-      <c r="CQ109" t="s">
-        <v>5</v>
-      </c>
-      <c r="CR109" t="s">
+      <c r="CT109" t="s">
+        <v>5</v>
+      </c>
+      <c r="CU109" t="s">
         <v>9</v>
       </c>
       <c r="DD109" t="s">
